--- a/outputs/Goat_percentile_classification_matrix.xlsx
+++ b/outputs/Goat_percentile_classification_matrix.xlsx
@@ -742,7 +742,7 @@
     <t>West Pokot</t>
   </si>
   <si>
-    <t>Minimal</t>
+    <t>No concern</t>
   </si>
   <si>
     <t>No data</t>
